--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B10" t="n">
-        <v>98228</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R10" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>98228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R11" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R12" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871844</v>
+        <v>125871873</v>
       </c>
       <c r="B18" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458038</v>
+        <v>458029</v>
       </c>
       <c r="R18" t="n">
-        <v>6841541</v>
+        <v>6841522</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871873</v>
+        <v>125871420</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458029</v>
+        <v>458022</v>
       </c>
       <c r="R19" t="n">
-        <v>6841522</v>
+        <v>6841591</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871420</v>
+        <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458022</v>
+        <v>458038</v>
       </c>
       <c r="R20" t="n">
-        <v>6841591</v>
+        <v>6841541</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R10" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>98228</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R11" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>98235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R12" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125870882</v>
+        <v>125870424</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>79046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458005</v>
+        <v>458012</v>
       </c>
       <c r="R14" t="n">
-        <v>6841415</v>
+        <v>6841298</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1956,32 +1956,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125870424</v>
+        <v>125871545</v>
       </c>
       <c r="B15" t="n">
-        <v>79046</v>
+        <v>98235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458012</v>
+        <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841298</v>
+        <v>6841603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125871545</v>
+        <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>98228</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         <v>458005</v>
       </c>
       <c r="R16" t="n">
-        <v>6841603</v>
+        <v>6841415</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871873</v>
+        <v>125871844</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458029</v>
+        <v>458038</v>
       </c>
       <c r="R18" t="n">
-        <v>6841522</v>
+        <v>6841541</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871420</v>
+        <v>125871873</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458022</v>
+        <v>458029</v>
       </c>
       <c r="R19" t="n">
-        <v>6841591</v>
+        <v>6841522</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871844</v>
+        <v>125871420</v>
       </c>
       <c r="B20" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458038</v>
+        <v>458022</v>
       </c>
       <c r="R20" t="n">
-        <v>6841541</v>
+        <v>6841591</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125870840</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125871897</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125871252</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125872038</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125871008</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125871387</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R10" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R11" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,7 +1663,7 @@
         <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>98235</v>
+        <v>98236</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>125870424</v>
       </c>
       <c r="B14" t="n">
-        <v>79046</v>
+        <v>79047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125871545</v>
+        <v>125870882</v>
       </c>
       <c r="B15" t="n">
-        <v>98235</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841603</v>
+        <v>6841415</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125870882</v>
+        <v>125871545</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         <v>458005</v>
       </c>
       <c r="R16" t="n">
-        <v>6841415</v>
+        <v>6841603</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>125871572</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871844</v>
+        <v>125871873</v>
       </c>
       <c r="B18" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458038</v>
+        <v>458029</v>
       </c>
       <c r="R18" t="n">
-        <v>6841541</v>
+        <v>6841522</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871873</v>
+        <v>125871420</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458029</v>
+        <v>458022</v>
       </c>
       <c r="R19" t="n">
-        <v>6841522</v>
+        <v>6841591</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871420</v>
+        <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458022</v>
+        <v>458038</v>
       </c>
       <c r="R20" t="n">
-        <v>6841591</v>
+        <v>6841541</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2541,7 +2541,7 @@
         <v>125871108</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R10" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R11" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,7 +1663,7 @@
         <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876535</v>
+        <v>125870424</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>79047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458035</v>
+        <v>458012</v>
       </c>
       <c r="R13" t="n">
-        <v>6841070</v>
+        <v>6841298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125870424</v>
+        <v>125876535</v>
       </c>
       <c r="B14" t="n">
-        <v>79047</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458012</v>
+        <v>458035</v>
       </c>
       <c r="R14" t="n">
-        <v>6841298</v>
+        <v>6841070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1959,7 +1959,7 @@
         <v>125870882</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>125871545</v>
       </c>
       <c r="B16" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1262,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125871008</v>
+        <v>125871387</v>
       </c>
       <c r="B8" t="n">
         <v>78968</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458003</v>
+        <v>458018</v>
       </c>
       <c r="R8" t="n">
-        <v>6841449</v>
+        <v>6841569</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande i området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125871387</v>
+        <v>125871008</v>
       </c>
       <c r="B9" t="n">
         <v>78968</v>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458018</v>
+        <v>458003</v>
       </c>
       <c r="R9" t="n">
-        <v>6841569</v>
+        <v>6841449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande i området.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>125870840</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125871897</v>
       </c>
       <c r="B4" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125871252</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125872038</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125871387</v>
+        <v>125871008</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458018</v>
+        <v>458003</v>
       </c>
       <c r="R8" t="n">
-        <v>6841569</v>
+        <v>6841449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande i området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125871008</v>
+        <v>125871387</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458003</v>
+        <v>458018</v>
       </c>
       <c r="R9" t="n">
-        <v>6841449</v>
+        <v>6841569</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande i området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>98242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R10" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R11" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B12" t="n">
-        <v>98238</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R12" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,7 +1760,7 @@
         <v>125870424</v>
       </c>
       <c r="B13" t="n">
-        <v>79047</v>
+        <v>79051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>125870882</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>125871545</v>
       </c>
       <c r="B16" t="n">
-        <v>98238</v>
+        <v>98242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>125871572</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871873</v>
+        <v>125871844</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458029</v>
+        <v>458038</v>
       </c>
       <c r="R18" t="n">
-        <v>6841522</v>
+        <v>6841541</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871420</v>
+        <v>125871873</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458022</v>
+        <v>458029</v>
       </c>
       <c r="R19" t="n">
-        <v>6841591</v>
+        <v>6841522</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871844</v>
+        <v>125871420</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458038</v>
+        <v>458022</v>
       </c>
       <c r="R20" t="n">
-        <v>6841541</v>
+        <v>6841591</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2541,7 +2541,7 @@
         <v>125871108</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R11" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R12" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871844</v>
+        <v>125871873</v>
       </c>
       <c r="B18" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458038</v>
+        <v>458029</v>
       </c>
       <c r="R18" t="n">
-        <v>6841541</v>
+        <v>6841522</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871873</v>
+        <v>125871420</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458029</v>
+        <v>458022</v>
       </c>
       <c r="R19" t="n">
-        <v>6841522</v>
+        <v>6841591</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871420</v>
+        <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458022</v>
+        <v>458038</v>
       </c>
       <c r="R20" t="n">
-        <v>6841591</v>
+        <v>6841541</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B10" t="n">
-        <v>98242</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R10" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R11" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>98243</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R12" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125870882</v>
+        <v>125871545</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841415</v>
+        <v>6841603</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125871545</v>
+        <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>98242</v>
+        <v>98360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         <v>458005</v>
       </c>
       <c r="R16" t="n">
-        <v>6841603</v>
+        <v>6841415</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R10" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>98243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R11" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B12" t="n">
-        <v>98243</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R12" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125875789</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125870840</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125871897</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125871252</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125872038</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125871008</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125871387</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R10" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1561,7 +1566,7 @@
         <v>125870755</v>
       </c>
       <c r="B11" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R12" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125870424</v>
+        <v>125876535</v>
       </c>
       <c r="B13" t="n">
-        <v>79051</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458012</v>
+        <v>458035</v>
       </c>
       <c r="R13" t="n">
-        <v>6841298</v>
+        <v>6841070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876535</v>
+        <v>125871545</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>98245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458035</v>
+        <v>458005</v>
       </c>
       <c r="R14" t="n">
-        <v>6841070</v>
+        <v>6841603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125871545</v>
+        <v>125870882</v>
       </c>
       <c r="B15" t="n">
-        <v>98243</v>
+        <v>98362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841603</v>
+        <v>6841415</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125870882</v>
+        <v>125870424</v>
       </c>
       <c r="B16" t="n">
-        <v>98360</v>
+        <v>79052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458005</v>
+        <v>458012</v>
       </c>
       <c r="R16" t="n">
-        <v>6841415</v>
+        <v>6841298</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>125871572</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>125871873</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>125871420</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>125871108</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>125875110</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R10" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>98245</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R11" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>98245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R12" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>98247</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R10" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R11" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B12" t="n">
-        <v>98245</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R12" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876535</v>
+        <v>125870424</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>79052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458035</v>
+        <v>458012</v>
       </c>
       <c r="R13" t="n">
-        <v>6841070</v>
+        <v>6841298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125871545</v>
+        <v>125876535</v>
       </c>
       <c r="B14" t="n">
-        <v>98245</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458005</v>
+        <v>458035</v>
       </c>
       <c r="R14" t="n">
-        <v>6841603</v>
+        <v>6841070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125870882</v>
+        <v>125871545</v>
       </c>
       <c r="B15" t="n">
-        <v>98362</v>
+        <v>98247</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841415</v>
+        <v>6841603</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125870424</v>
+        <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>79052</v>
+        <v>98364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458012</v>
+        <v>458005</v>
       </c>
       <c r="R16" t="n">
-        <v>6841298</v>
+        <v>6841415</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871873</v>
+        <v>125871420</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458029</v>
+        <v>458022</v>
       </c>
       <c r="R18" t="n">
-        <v>6841522</v>
+        <v>6841591</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871420</v>
+        <v>125871844</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458022</v>
+        <v>458038</v>
       </c>
       <c r="R19" t="n">
-        <v>6841591</v>
+        <v>6841541</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871844</v>
+        <v>125871873</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458038</v>
+        <v>458029</v>
       </c>
       <c r="R20" t="n">
-        <v>6841541</v>
+        <v>6841522</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870755</v>
+        <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>98247</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458002</v>
+        <v>458000</v>
       </c>
       <c r="R10" t="n">
-        <v>6841392</v>
+        <v>6841426</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R11" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876409</v>
+        <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>98247</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458018</v>
+        <v>458002</v>
       </c>
       <c r="R12" t="n">
-        <v>6841063</v>
+        <v>6841392</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125870424</v>
+        <v>125876535</v>
       </c>
       <c r="B13" t="n">
-        <v>79052</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458012</v>
+        <v>458035</v>
       </c>
       <c r="R13" t="n">
-        <v>6841298</v>
+        <v>6841070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876535</v>
+        <v>125871545</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>98247</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458035</v>
+        <v>458005</v>
       </c>
       <c r="R14" t="n">
-        <v>6841070</v>
+        <v>6841603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,32 +1956,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125871545</v>
+        <v>125870424</v>
       </c>
       <c r="B15" t="n">
-        <v>98247</v>
+        <v>79052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458005</v>
+        <v>458012</v>
       </c>
       <c r="R15" t="n">
-        <v>6841603</v>
+        <v>6841298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876535</v>
+        <v>125870424</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>79052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458035</v>
+        <v>458012</v>
       </c>
       <c r="R13" t="n">
-        <v>6841070</v>
+        <v>6841298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125871545</v>
+        <v>125876535</v>
       </c>
       <c r="B14" t="n">
-        <v>98247</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458005</v>
+        <v>458035</v>
       </c>
       <c r="R14" t="n">
-        <v>6841603</v>
+        <v>6841070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,32 +1956,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125870424</v>
+        <v>125871545</v>
       </c>
       <c r="B15" t="n">
-        <v>79052</v>
+        <v>98249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458012</v>
+        <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841298</v>
+        <v>6841603</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
         <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871420</v>
+        <v>125871873</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458022</v>
+        <v>458029</v>
       </c>
       <c r="R18" t="n">
-        <v>6841591</v>
+        <v>6841522</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871844</v>
+        <v>125871420</v>
       </c>
       <c r="B19" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458038</v>
+        <v>458022</v>
       </c>
       <c r="R19" t="n">
-        <v>6841541</v>
+        <v>6841591</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871873</v>
+        <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458029</v>
+        <v>458038</v>
       </c>
       <c r="R20" t="n">
-        <v>6841522</v>
+        <v>6841541</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125875789</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125870840</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125871897</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125871252</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125872038</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125871008</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125871387</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>125870424</v>
       </c>
       <c r="B13" t="n">
-        <v>79052</v>
+        <v>79056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>125876535</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>125871545</v>
       </c>
       <c r="B15" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>125871572</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>125871873</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>125871420</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>125871108</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>125875110</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R10" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1574,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1598,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R11" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,11 +1634,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125870424</v>
+        <v>125876535</v>
       </c>
       <c r="B13" t="n">
-        <v>79056</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458012</v>
+        <v>458035</v>
       </c>
       <c r="R13" t="n">
-        <v>6841298</v>
+        <v>6841070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876535</v>
+        <v>125870424</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>79056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458035</v>
+        <v>458012</v>
       </c>
       <c r="R14" t="n">
-        <v>6841070</v>
+        <v>6841298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R10" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R11" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1634,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,7 +1663,7 @@
         <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>125871545</v>
       </c>
       <c r="B15" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870907</v>
+        <v>125870755</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>98256</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458000</v>
+        <v>458002</v>
       </c>
       <c r="R10" t="n">
-        <v>6841426</v>
+        <v>6841392</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876409</v>
+        <v>125870907</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458018</v>
+        <v>458000</v>
       </c>
       <c r="R11" t="n">
-        <v>6841063</v>
+        <v>6841426</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870755</v>
+        <v>125876409</v>
       </c>
       <c r="B12" t="n">
-        <v>98256</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458002</v>
+        <v>458018</v>
       </c>
       <c r="R12" t="n">
-        <v>6841392</v>
+        <v>6841063</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871873</v>
+        <v>125871844</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458029</v>
+        <v>458038</v>
       </c>
       <c r="R18" t="n">
-        <v>6841522</v>
+        <v>6841541</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871420</v>
+        <v>125871873</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458022</v>
+        <v>458029</v>
       </c>
       <c r="R19" t="n">
-        <v>6841591</v>
+        <v>6841522</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871844</v>
+        <v>125871420</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458038</v>
+        <v>458022</v>
       </c>
       <c r="R20" t="n">
-        <v>6841541</v>
+        <v>6841591</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870755</v>
+        <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>98256</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458002</v>
+        <v>458000</v>
       </c>
       <c r="R10" t="n">
-        <v>6841392</v>
+        <v>6841426</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125870907</v>
+        <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458000</v>
+        <v>458018</v>
       </c>
       <c r="R11" t="n">
-        <v>6841426</v>
+        <v>6841063</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125876409</v>
+        <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>98256</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458018</v>
+        <v>458002</v>
       </c>
       <c r="R12" t="n">
-        <v>6841063</v>
+        <v>6841392</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876535</v>
+        <v>125870424</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>79056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458035</v>
+        <v>458012</v>
       </c>
       <c r="R13" t="n">
-        <v>6841070</v>
+        <v>6841298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125870424</v>
+        <v>125876535</v>
       </c>
       <c r="B14" t="n">
-        <v>79056</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458012</v>
+        <v>458035</v>
       </c>
       <c r="R14" t="n">
-        <v>6841298</v>
+        <v>6841070</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1930,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125871545</v>
+        <v>125870882</v>
       </c>
       <c r="B15" t="n">
-        <v>98256</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841603</v>
+        <v>6841415</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125870882</v>
+        <v>125871545</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>98256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         <v>458005</v>
       </c>
       <c r="R16" t="n">
-        <v>6841415</v>
+        <v>6841603</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871844</v>
+        <v>125871873</v>
       </c>
       <c r="B18" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458038</v>
+        <v>458029</v>
       </c>
       <c r="R18" t="n">
-        <v>6841541</v>
+        <v>6841522</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871873</v>
+        <v>125871420</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458029</v>
+        <v>458022</v>
       </c>
       <c r="R19" t="n">
-        <v>6841522</v>
+        <v>6841591</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871420</v>
+        <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458022</v>
+        <v>458038</v>
       </c>
       <c r="R20" t="n">
-        <v>6841591</v>
+        <v>6841541</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871873</v>
+        <v>125871844</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458029</v>
+        <v>458038</v>
       </c>
       <c r="R18" t="n">
-        <v>6841522</v>
+        <v>6841541</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871420</v>
+        <v>125871873</v>
       </c>
       <c r="B19" t="n">
         <v>78977</v>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458022</v>
+        <v>458029</v>
       </c>
       <c r="R19" t="n">
-        <v>6841591</v>
+        <v>6841522</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871844</v>
+        <v>125871420</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458038</v>
+        <v>458022</v>
       </c>
       <c r="R20" t="n">
-        <v>6841541</v>
+        <v>6841591</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125875789</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125870840</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125871897</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125871252</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125872038</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125871238</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125871008</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125871387</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>125870907</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>125876409</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>125870755</v>
       </c>
       <c r="B12" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125870424</v>
+        <v>125876535</v>
       </c>
       <c r="B13" t="n">
-        <v>79056</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458012</v>
+        <v>458035</v>
       </c>
       <c r="R13" t="n">
-        <v>6841298</v>
+        <v>6841070</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1828,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876535</v>
+        <v>125870424</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>79059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458035</v>
+        <v>458012</v>
       </c>
       <c r="R14" t="n">
-        <v>6841070</v>
+        <v>6841298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1925,11 +1930,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1956,10 +1956,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125870882</v>
+        <v>125871545</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98265</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1967,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         <v>458005</v>
       </c>
       <c r="R15" t="n">
-        <v>6841415</v>
+        <v>6841603</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125871545</v>
+        <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>98256</v>
+        <v>98382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         <v>458005</v>
       </c>
       <c r="R16" t="n">
-        <v>6841603</v>
+        <v>6841415</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>125871572</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871844</v>
+        <v>125871873</v>
       </c>
       <c r="B18" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,13 +2282,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458038</v>
+        <v>458029</v>
       </c>
       <c r="R18" t="n">
-        <v>6841541</v>
+        <v>6841522</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871873</v>
+        <v>125871420</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,13 +2379,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458029</v>
+        <v>458022</v>
       </c>
       <c r="R19" t="n">
-        <v>6841522</v>
+        <v>6841591</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871420</v>
+        <v>125871844</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458022</v>
+        <v>458038</v>
       </c>
       <c r="R20" t="n">
-        <v>6841591</v>
+        <v>6841541</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2541,7 +2541,7 @@
         <v>125871108</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>125870544</v>
       </c>
       <c r="B22" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>125875110</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125876535</v>
+        <v>125870424</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>79059</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458035</v>
+        <v>458012</v>
       </c>
       <c r="R13" t="n">
-        <v>6841070</v>
+        <v>6841298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1859,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125870424</v>
+        <v>125870882</v>
       </c>
       <c r="B14" t="n">
-        <v>79059</v>
+        <v>98382</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,13 +1889,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458012</v>
+        <v>458005</v>
       </c>
       <c r="R14" t="n">
-        <v>6841298</v>
+        <v>6841415</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125870882</v>
+        <v>125876535</v>
       </c>
       <c r="B16" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,13 +2083,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458005</v>
+        <v>458035</v>
       </c>
       <c r="R16" t="n">
-        <v>6841415</v>
+        <v>6841070</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2124,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125870882</v>
+        <v>125876535</v>
       </c>
       <c r="B14" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458005</v>
+        <v>458035</v>
       </c>
       <c r="R14" t="n">
-        <v>6841415</v>
+        <v>6841070</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1925,6 +1925,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2048,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125876535</v>
+        <v>125870882</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,13 +2088,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458035</v>
+        <v>458005</v>
       </c>
       <c r="R16" t="n">
-        <v>6841070</v>
+        <v>6841415</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2119,11 +2124,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125875789</v>
+        <v>125870424</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458021</v>
+        <v>458012</v>
       </c>
       <c r="R2" t="n">
-        <v>6841077</v>
+        <v>6841298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125870840</v>
+        <v>125871897</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458009</v>
+        <v>458027</v>
       </c>
       <c r="R3" t="n">
-        <v>6841407</v>
+        <v>6841488</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125871897</v>
+        <v>125870840</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458027</v>
+        <v>458009</v>
       </c>
       <c r="R4" t="n">
-        <v>6841488</v>
+        <v>6841407</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125871252</v>
+        <v>125870907</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1006,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458003</v>
+        <v>458000</v>
       </c>
       <c r="R5" t="n">
-        <v>6841528</v>
+        <v>6841426</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125872038</v>
+        <v>125871008</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458062</v>
+        <v>458003</v>
       </c>
       <c r="R6" t="n">
-        <v>6841220</v>
+        <v>6841449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125871238</v>
+        <v>125871108</v>
       </c>
       <c r="B7" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458003</v>
+        <v>458000</v>
       </c>
       <c r="R7" t="n">
-        <v>6841528</v>
+        <v>6841463</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125871008</v>
+        <v>125871252</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1300,7 +1295,7 @@
         <v>458003</v>
       </c>
       <c r="R8" t="n">
-        <v>6841449</v>
+        <v>6841528</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,11 +1357,11 @@
         <v>125871387</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1461,14 +1456,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125870907</v>
+        <v>125871420</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458000</v>
+        <v>458022</v>
       </c>
       <c r="R10" t="n">
-        <v>6841426</v>
+        <v>6841591</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1558,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125876409</v>
+        <v>125871572</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,13 +1588,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458018</v>
+        <v>458011</v>
       </c>
       <c r="R11" t="n">
-        <v>6841063</v>
+        <v>6841620</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1629,11 +1624,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125870755</v>
+        <v>125871873</v>
       </c>
       <c r="B12" t="n">
-        <v>98265</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458002</v>
+        <v>458029</v>
       </c>
       <c r="R12" t="n">
-        <v>6841392</v>
+        <v>6841522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125870424</v>
+        <v>125872038</v>
       </c>
       <c r="B13" t="n">
-        <v>79059</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458012</v>
+        <v>458062</v>
       </c>
       <c r="R13" t="n">
-        <v>6841298</v>
+        <v>6841220</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125876535</v>
+        <v>125875110</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458035</v>
+        <v>458007</v>
       </c>
       <c r="R14" t="n">
-        <v>6841070</v>
+        <v>6841069</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125871545</v>
+        <v>125875789</v>
       </c>
       <c r="B15" t="n">
-        <v>98265</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458005</v>
+        <v>458021</v>
       </c>
       <c r="R15" t="n">
-        <v>6841603</v>
+        <v>6841077</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2027,6 +2017,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125870882</v>
+        <v>125876409</v>
       </c>
       <c r="B16" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,13 +2083,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458005</v>
+        <v>458018</v>
       </c>
       <c r="R16" t="n">
-        <v>6841415</v>
+        <v>6841063</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2124,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125871572</v>
+        <v>125876535</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458011</v>
+        <v>458035</v>
       </c>
       <c r="R17" t="n">
-        <v>6841620</v>
+        <v>6841070</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2221,6 +2221,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,32 +2252,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125871873</v>
+        <v>125870755</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>99022</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>458029</v>
+        <v>458002</v>
       </c>
       <c r="R18" t="n">
-        <v>6841522</v>
+        <v>6841392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125871420</v>
+        <v>125871545</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>99022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,13 +2384,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458022</v>
+        <v>458005</v>
       </c>
       <c r="R19" t="n">
-        <v>6841591</v>
+        <v>6841603</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2441,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125871844</v>
+        <v>125870544</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,13 +2481,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>458038</v>
+        <v>458026</v>
       </c>
       <c r="R20" t="n">
-        <v>6841541</v>
+        <v>6841339</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2538,32 +2543,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125871108</v>
+        <v>125870882</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>99140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,13 +2578,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>458000</v>
+        <v>458005</v>
       </c>
       <c r="R21" t="n">
-        <v>6841463</v>
+        <v>6841415</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2635,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125870544</v>
+        <v>125871238</v>
       </c>
       <c r="B22" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>458026</v>
+        <v>458003</v>
       </c>
       <c r="R22" t="n">
-        <v>6841339</v>
+        <v>6841528</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125875110</v>
+        <v>125871844</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2743,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2767,13 +2772,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>458007</v>
+        <v>458038</v>
       </c>
       <c r="R23" t="n">
-        <v>6841069</v>
+        <v>6841541</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2803,11 +2808,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 35454-2024 artfynd.xlsx
+++ b/artfynd/A 35454-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870424</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870907</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871008</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871108</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871252</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871387</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871572</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871873</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125872038</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125875110</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125875789</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125876409</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125876535</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2346,6 +2431,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870755</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2443,6 +2533,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871545</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870544</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125870882</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871238</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,8 +2941,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871844</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>